--- a/data/trans_orig/CAGE_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/CAGE_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2007</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>969</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265329</t>
+          <t>265479</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272086</t>
+          <t>273010</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>255848</t>
+          <t>256275</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>524342</t>
+          <t>525128</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>532882</t>
+          <t>532879</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13340</t>
+          <t>13751</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12788</t>
+          <t>13161</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479735</t>
+          <t>479324</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>490116</t>
+          <t>490126</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>502014</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503949</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>984236</t>
+          <t>983863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>994179</t>
+          <t>994162</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,97 +1419,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1916</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>1945</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316878</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335412</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>652313</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>654258</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13727</t>
+          <t>13581</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17134</t>
+          <t>16473</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>344944</t>
+          <t>345090</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356706</t>
+          <t>356636</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>362559</t>
+          <t>363472</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>712993</t>
+          <t>713654</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>726359</t>
+          <t>727110</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197919</t>
+          <t>198431</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199407</t>
+          <t>199553</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>401310</t>
+          <t>400740</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>10945</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12315</t>
+          <t>13721</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261441</t>
+          <t>259866</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>272089</t>
+          <t>270920</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>536640</t>
+          <t>535234</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>547926</t>
+          <t>547230</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>607702</t>
+          <t>606615</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>636249</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>638219</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1244237</t>
+          <t>1245624</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8748</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11573</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>735047</t>
+          <t>735038</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>742915</t>
+          <t>742907</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>776992</t>
+          <t>776106</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1515700</t>
+          <t>1515733</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1524756</t>
+          <t>1525353</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17045</t>
+          <t>17014</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38902</t>
+          <t>38046</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>18367</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,47 +3527,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>34927</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>24204</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>47707</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>34927</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>24809</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>48344</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3237641</t>
+          <t>3238497</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3259498</t>
+          <t>3259529</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3361538</t>
+          <t>3360830</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3375477</t>
+          <t>3374871</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,47 +3640,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>99,87%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6620814</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6608034</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6631537</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,89%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6620814</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6607397</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6630932</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2012</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>15479</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32252</t>
+          <t>33886</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>15129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34840</t>
+          <t>36517</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262486</t>
+          <t>260852</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>280512</t>
+          <t>279259</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282587</t>
+          <t>281631</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>547143</t>
+          <t>545466</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>566475</t>
+          <t>566854</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20421</t>
+          <t>21466</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21430</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>485106</t>
+          <t>484061</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500072</t>
+          <t>499790</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>521674</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>523765</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1007862</t>
+          <t>1007112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1023484</t>
+          <t>1024075</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -4742,97 +4742,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1944</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5592</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>986</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5194</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5997</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>986</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4308</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>322102</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324046</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>335826</t>
+          <t>335428</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>660758</t>
+          <t>659069</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,62 +5120,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3716</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5294</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>369068</t>
+          <t>368928</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>386944</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>388951</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>757639</t>
+          <t>759217</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199812</t>
+          <t>200014</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209806</t>
+          <t>210269</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>217613</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>219591</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>419895</t>
+          <t>419235</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>429892</t>
+          <t>429329</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,47 +5806,47 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268157</t>
+          <t>268682</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>278040</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>280031</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>548669</t>
+          <t>548712</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>6445</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21602</t>
+          <t>21634</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23261</t>
+          <t>24468</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>641186</t>
+          <t>641154</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>656873</t>
+          <t>656343</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>687232</t>
+          <t>687029</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1333380</t>
+          <t>1332173</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1348987</t>
+          <t>1348692</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22232</t>
+          <t>22887</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23115</t>
+          <t>24321</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>756866</t>
+          <t>756211</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>773216</t>
+          <t>773907</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>818883</t>
+          <t>818867</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1579836</t>
+          <t>1578630</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1596886</t>
+          <t>1596573</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50279</t>
+          <t>50005</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>85946</t>
+          <t>84334</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11405</t>
+          <t>11445</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>55135</t>
+          <t>55382</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>91422</t>
+          <t>90084</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3340833</t>
+          <t>3342445</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3376500</t>
+          <t>3376774</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3546904</t>
+          <t>3546864</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3556323</t>
+          <t>3556320</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6893666</t>
+          <t>6895004</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6929953</t>
+          <t>6929706</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2016</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8770</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25504</t>
+          <t>24446</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14117</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>32616</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>268257</t>
+          <t>269315</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284991</t>
+          <t>285438</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274586</t>
+          <t>274268</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286664</t>
+          <t>286029</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>550920</t>
+          <t>549848</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>569933</t>
+          <t>569341</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10023</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11948</t>
+          <t>12125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>492552</t>
+          <t>491662</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501452</t>
+          <t>501456</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>517532</t>
+          <t>516369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1013711</t>
+          <t>1013534</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1023521</t>
+          <t>1023572</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,62 +8100,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1939</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4354</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3969</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313741</t>
+          <t>315061</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>334370</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>336309</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>650905</t>
+          <t>650520</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,62 +8443,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2071</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>7606</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>363182</t>
+          <t>363117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>385212</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387283</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>751309</t>
+          <t>749641</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7572</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>934</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203489</t>
+          <t>203649</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210281</t>
+          <t>210287</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>216714</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218587</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>422178</t>
+          <t>422153</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428877</t>
+          <t>428874</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>903</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t>8517</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256076</t>
+          <t>256362</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>267754</t>
+          <t>267544</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>527697</t>
+          <t>527721</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>535336</t>
+          <t>535335</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9723</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27049</t>
+          <t>28748</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13726</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13627</t>
+          <t>14312</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35021</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>629509</t>
+          <t>627810</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>646835</t>
+          <t>646437</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>677568</t>
+          <t>679019</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>689179</t>
+          <t>689160</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1312831</t>
+          <t>1312436</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1334225</t>
+          <t>1333540</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>14844</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>767409</t>
+          <t>766533</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776611</t>
+          <t>776687</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>818414</t>
+          <t>819094</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1590057</t>
+          <t>1589906</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1601633</t>
+          <t>1601615</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36392</t>
+          <t>36011</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>65896</t>
+          <t>65692</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>28031</t>
+          <t>27129</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>51351</t>
+          <t>50398</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>85316</t>
+          <t>83590</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3328454</t>
+          <t>3328658</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3357958</t>
+          <t>3358339</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3516511</t>
+          <t>3517413</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3534797</t>
+          <t>3534672</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6853576</t>
+          <t>6855302</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6887541</t>
+          <t>6888494</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2023</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>2284</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16321</t>
+          <t>16986</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163568</t>
+          <t>162903</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>178296</t>
+          <t>177605</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89622</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>254368</t>
+          <t>254289</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>268923</t>
+          <t>268982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -11045,97 +11045,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2729</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1510</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2202</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>247621</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>250350</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>107174</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108684</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>356831</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16826</t>
+          <t>16007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>446</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18625</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168360</t>
+          <t>169179</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180018</t>
+          <t>180564</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85826</t>
+          <t>85385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89834</t>
+          <t>89826</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>256833</t>
+          <t>257642</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>269388</t>
+          <t>269224</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -11731,62 +11731,62 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6770</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6850</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3021</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>902</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170627</t>
+          <t>170707</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>176760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,49 +11859,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>123443</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>121324</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>124345</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>123443</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>121039</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>124345</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>335</t>
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>293402</t>
+          <t>294361</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>300571</t>
+          <t>300774</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -12074,97 +12074,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2046</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>23,83%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>440</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2375</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2437</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37292</t>
+          <t>37239</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>552</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12466</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155235</t>
+          <t>155678</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>163109</t>
+          <t>163380</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90595</t>
+          <t>90285</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95894</t>
+          <t>95868</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>249002</t>
+          <t>249374</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>258312</t>
+          <t>258402</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17063</t>
+          <t>16916</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18610</t>
+          <t>18343</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6224</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28808</t>
+          <t>28603</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>290867</t>
+          <t>291014</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>303104</t>
+          <t>303237</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>380863</t>
+          <t>381130</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>398935</t>
+          <t>398844</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>678595</t>
+          <t>678800</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>701179</t>
+          <t>701655</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2284</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>267560</t>
+          <t>267033</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>275587</t>
+          <t>275496</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>93453</t>
+          <t>94757</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>364983</t>
+          <t>364905</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>373607</t>
+          <t>373328</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24755</t>
+          <t>25905</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48734</t>
+          <t>50138</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22683</t>
+          <t>24072</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>34586</t>
+          <t>32694</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>64109</t>
+          <t>64580</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1524803</t>
+          <t>1523399</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1548782</t>
+          <t>1547632</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>994878</t>
+          <t>993489</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1011772</t>
+          <t>1011904</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2526989</t>
+          <t>2526518</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2556512</t>
+          <t>2558404</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CAGE_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/CAGE_R-Provincia-trans_orig.xlsx
@@ -733,62 +733,62 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7522</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7531</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4981</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>988</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4563</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>959</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265479</t>
+          <t>265488</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>273010</t>
+          <t>272086</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,44 +866,44 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>259850</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>255857</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>260838</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>259850</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>256275</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>260838</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>512</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>525128</t>
+          <t>524323</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>532879</t>
+          <t>532889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13751</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>13475</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479324</t>
+          <t>479748</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>490126</t>
+          <t>490058</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>983863</t>
+          <t>983549</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>994162</t>
+          <t>994068</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13581</t>
+          <t>13893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>17038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>345090</t>
+          <t>344778</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356636</t>
+          <t>356629</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>363472</t>
+          <t>361584</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>713654</t>
+          <t>713089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>727110</t>
+          <t>726689</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8115</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198431</t>
+          <t>198760</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199553</t>
+          <t>199402</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>400740</t>
+          <t>402624</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10945</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13721</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259866</t>
+          <t>259774</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270920</t>
+          <t>271093</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>535234</t>
+          <t>537245</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>547230</t>
+          <t>547925</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>847</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>849</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>606615</t>
+          <t>607752</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>614177</t>
+          <t>614180</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1245624</t>
+          <t>1245464</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1252396</t>
+          <t>1252397</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11573</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>735038</t>
+          <t>734822</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>742907</t>
+          <t>742914</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>776106</t>
+          <t>776384</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1515733</t>
+          <t>1515289</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1525353</t>
+          <t>1525152</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>16852</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38046</t>
+          <t>37973</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,82 +3492,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>9289</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>4632</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>18511</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>34927</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>24974</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>48973</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>9289</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>4326</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>18367</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>34927</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>24204</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>47707</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3238497</t>
+          <t>3238570</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3259529</t>
+          <t>3259691</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3610,77 +3610,77 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3289</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3369908</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3360686</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3374565</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6620814</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6606768</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6630767</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3289</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3369908</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>3360830</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3374871</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6620814</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6608034</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6631537</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15479</t>
+          <t>15393</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33886</t>
+          <t>33210</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15129</t>
+          <t>15133</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36517</t>
+          <t>35410</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260852</t>
+          <t>261528</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279259</t>
+          <t>279345</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281631</t>
+          <t>281983</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>545466</t>
+          <t>546573</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>566854</t>
+          <t>566850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5799</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21466</t>
+          <t>21635</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22180</t>
+          <t>21143</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>484061</t>
+          <t>483892</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499790</t>
+          <t>499728</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1007112</t>
+          <t>1008149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1024075</t>
+          <t>1023197</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>335428</t>
+          <t>336099</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>659069</t>
+          <t>661100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>368928</t>
+          <t>369376</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>759217</t>
+          <t>757810</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12974</t>
+          <t>13571</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>200014</t>
+          <t>199865</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210269</t>
+          <t>210143</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>419235</t>
+          <t>418638</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>429329</t>
+          <t>429569</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268682</t>
+          <t>268706</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>548712</t>
+          <t>548715</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21634</t>
+          <t>21878</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24468</t>
+          <t>23784</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>641154</t>
+          <t>640910</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>656343</t>
+          <t>656868</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>687029</t>
+          <t>687248</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1332173</t>
+          <t>1332857</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1348692</t>
+          <t>1348660</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22887</t>
+          <t>23537</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24321</t>
+          <t>23295</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>756211</t>
+          <t>755561</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>773907</t>
+          <t>773023</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>818867</t>
+          <t>819837</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1578630</t>
+          <t>1579656</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1596573</t>
+          <t>1596978</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50005</t>
+          <t>49698</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>84334</t>
+          <t>84873</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11445</t>
+          <t>12225</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>55382</t>
+          <t>55520</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>90084</t>
+          <t>90574</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3342445</t>
+          <t>3341906</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3376774</t>
+          <t>3377081</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3546864</t>
+          <t>3546084</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3556320</t>
+          <t>3556330</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6895004</t>
+          <t>6894514</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6929706</t>
+          <t>6929568</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24446</t>
+          <t>26004</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14435</t>
+          <t>14667</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32616</t>
+          <t>33481</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269315</t>
+          <t>267757</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>285438</t>
+          <t>285614</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274268</t>
+          <t>274036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286029</t>
+          <t>285973</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>549848</t>
+          <t>548983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>569341</t>
+          <t>568906</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>12117</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491662</t>
+          <t>492710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501456</t>
+          <t>501464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>516369</t>
+          <t>516760</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1013534</t>
+          <t>1013542</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1023572</t>
+          <t>1023515</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>315061</t>
+          <t>313297</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>650520</t>
+          <t>650724</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>363117</t>
+          <t>362111</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>749641</t>
+          <t>750879</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>943</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203649</t>
+          <t>203553</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210287</t>
+          <t>210286</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>422153</t>
+          <t>422090</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428874</t>
+          <t>428865</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>890</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256362</t>
+          <t>256460</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>267544</t>
+          <t>268350</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>527721</t>
+          <t>528633</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>535335</t>
+          <t>535348</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28748</t>
+          <t>28728</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>35279</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>627810</t>
+          <t>627830</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>646437</t>
+          <t>646661</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>679019</t>
+          <t>678976</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>689160</t>
+          <t>689202</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1312436</t>
+          <t>1312573</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1333540</t>
+          <t>1333866</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12050</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14844</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>766533</t>
+          <t>766501</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776687</t>
+          <t>776646</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>819094</t>
+          <t>818471</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1589906</t>
+          <t>1590404</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1601615</t>
+          <t>1601685</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36011</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>65692</t>
+          <t>64060</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27129</t>
+          <t>26200</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>50398</t>
+          <t>51207</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>83590</t>
+          <t>83935</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3328658</t>
+          <t>3330290</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3358339</t>
+          <t>3358349</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3517413</t>
+          <t>3518342</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3534672</t>
+          <t>3535282</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6855302</t>
+          <t>6854957</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6888494</t>
+          <t>6887685</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16986</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>12661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>173564</t>
+          <t>164979</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>162903</t>
+          <t>158070</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>177605</t>
+          <t>168608</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>264247</t>
+          <t>262210</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>254289</t>
+          <t>254469</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>268982</t>
+          <t>265831</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>250350</t>
+          <t>253429</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>108684</t>
+          <t>114633</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>359033</t>
+          <t>368062</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>250350</t>
+          <t>253429</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>250350</t>
+          <t>253429</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>250350</t>
+          <t>253429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>108684</t>
+          <t>114633</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>108684</t>
+          <t>114633</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>108684</t>
+          <t>114633</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>359033</t>
+          <t>368062</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>359033</t>
+          <t>368062</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>359033</t>
+          <t>368062</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,69 +11383,69 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16007</t>
+          <t>18123</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4401</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>4,93%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1683</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4887</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>16</t>
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17816</t>
+          <t>21143</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -11496,67 +11496,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>176061</t>
+          <t>176240</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>169179</t>
+          <t>169190</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180564</t>
+          <t>181432</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>87498</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>84810</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>88792</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,08%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>95,07%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,36%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>88589</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>85385</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>89826</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,14%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>264650</t>
+          <t>263737</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>257642</t>
+          <t>255380</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>269224</t>
+          <t>268809</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>692</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>979</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -11771,12 +11771,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,22 +11796,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>174979</t>
+          <t>200212</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170707</t>
+          <t>195597</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176760</t>
+          <t>201961</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,27 +11874,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>123443</t>
+          <t>137387</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121324</t>
+          <t>134733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11909,27 +11909,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>298422</t>
+          <t>337599</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>294361</t>
+          <t>333057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>300774</t>
+          <t>339831</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>202653</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>202653</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>202653</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>301822</t>
+          <t>341019</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>301822</t>
+          <t>341019</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>301822</t>
+          <t>341019</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -12217,27 +12217,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>10376</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12252,27 +12252,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>39289</t>
+          <t>44513</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37239</t>
+          <t>42510</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>546</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,27 +12482,27 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>12080</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>160512</t>
+          <t>158668</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155678</t>
+          <t>153943</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>163380</t>
+          <t>161399</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>94204</t>
+          <t>95963</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90285</t>
+          <t>91981</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95868</t>
+          <t>97648</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,22 +12595,22 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>254716</t>
+          <t>254631</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>249374</t>
+          <t>249087</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>258402</t>
+          <t>258037</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9216</t>
+          <t>14493</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16916</t>
+          <t>26140</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>9693</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>20202</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>15942</t>
+          <t>24187</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28603</t>
+          <t>37925</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>298714</t>
+          <t>335212</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>291014</t>
+          <t>323565</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>303237</t>
+          <t>342119</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>392747</t>
+          <t>223987</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>381130</t>
+          <t>213478</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>398844</t>
+          <t>229809</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>691461</t>
+          <t>559198</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>678800</t>
+          <t>545460</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>701655</t>
+          <t>568166</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>399473</t>
+          <t>233680</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>399473</t>
+          <t>233680</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>399473</t>
+          <t>233680</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707403</t>
+          <t>583385</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707403</t>
+          <t>583385</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707403</t>
+          <t>583385</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,102 +13098,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9479</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5396</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>5540</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>1902</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>11722</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1392</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4344</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>4997</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>2284</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>10707</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -13211,102 +13211,102 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>272907</t>
+          <t>309214</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>267033</t>
+          <t>303758</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>275496</t>
+          <t>312085</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>96,99%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>112605</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>108770</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>114166</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>95,27%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>421821</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>415639</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>425459</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>98,7%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>96,57%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>97709</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>94757</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>99101</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>95,62%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>370615</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>364905</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>373328</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>276512</t>
+          <t>313194</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>276512</t>
+          <t>313194</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>276512</t>
+          <t>313194</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>99101</t>
+          <t>114166</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>99101</t>
+          <t>114166</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>99101</t>
+          <t>114166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>375612</t>
+          <t>427361</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>375612</t>
+          <t>427361</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>375612</t>
+          <t>427361</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>41211</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25905</t>
+          <t>29825</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>50138</t>
+          <t>55525</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24072</t>
+          <t>28483</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t>57858</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>32694</t>
+          <t>44071</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>64580</t>
+          <t>74386</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1538231</t>
+          <t>1632092</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1523399</t>
+          <t>1617778</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1547632</t>
+          <t>1643478</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1004202</t>
+          <t>879679</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>993489</t>
+          <t>867843</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1011904</t>
+          <t>886578</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2542434</t>
+          <t>2511770</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2526518</t>
+          <t>2495242</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2558404</t>
+          <t>2525557</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
